--- a/surgical_staging/STAGED_CRS620MI_Suppliers.xlsx
+++ b/surgical_staging/STAGED_CRS620MI_Suppliers.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="238" uniqueCount="112">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="272" uniqueCount="122">
   <si>
     <t>IDCONO</t>
   </si>
@@ -130,6 +130,9 @@
     <t xml:space="preserve">500970    </t>
   </si>
   <si>
+    <t xml:space="preserve">501013    </t>
+  </si>
+  <si>
     <t xml:space="preserve">501023    </t>
   </si>
   <si>
@@ -151,6 +154,9 @@
     <t xml:space="preserve">Soarus, L.L.C.                      </t>
   </si>
   <si>
+    <t xml:space="preserve">Stonhard                            </t>
+  </si>
+  <si>
     <t xml:space="preserve">Sun Chemical Corp                   </t>
   </si>
   <si>
@@ -169,6 +175,9 @@
     <t xml:space="preserve">SOARUS    </t>
   </si>
   <si>
+    <t xml:space="preserve">STONHARD  </t>
+  </si>
+  <si>
     <t xml:space="preserve">SUN CHEM  </t>
   </si>
   <si>
@@ -184,6 +193,9 @@
     <t xml:space="preserve">           </t>
   </si>
   <si>
+    <t xml:space="preserve">560184790  </t>
+  </si>
+  <si>
     <t xml:space="preserve">222761297  </t>
   </si>
   <si>
@@ -208,6 +220,9 @@
     <t xml:space="preserve">(847) 255-1211  </t>
   </si>
   <si>
+    <t xml:space="preserve">(770) 425-9215  </t>
+  </si>
+  <si>
     <t xml:space="preserve">(404) 355-4131  </t>
   </si>
   <si>
@@ -226,6 +241,9 @@
     <t xml:space="preserve">(847) 255-4343  </t>
   </si>
   <si>
+    <t xml:space="preserve">(770) 425-6215  </t>
+  </si>
+  <si>
     <t xml:space="preserve">(404) 355-8741  </t>
   </si>
   <si>
@@ -298,6 +316,9 @@
     <t>141519.0</t>
   </si>
   <si>
+    <t>141523.0</t>
+  </si>
+  <si>
     <t>141524.0</t>
   </si>
   <si>
@@ -316,6 +337,9 @@
     <t>20230814.0</t>
   </si>
   <si>
+    <t>20050127.0</t>
+  </si>
+  <si>
     <t>20251204.0</t>
   </si>
   <si>
@@ -331,6 +355,9 @@
     <t>90.0</t>
   </si>
   <si>
+    <t>75.0</t>
+  </si>
+  <si>
     <t>83.0</t>
   </si>
   <si>
@@ -344,6 +371,9 @@
   </si>
   <si>
     <t xml:space="preserve">W20ACCAE  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">W20ACSNE  </t>
   </si>
   <si>
     <t xml:space="preserve">W70MEFOR  </t>
@@ -707,7 +737,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AH7"/>
+  <dimension ref="A1:AH8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:34">
@@ -822,100 +852,100 @@
         <v>35</v>
       </c>
       <c r="C2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="F2" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="G2" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="H2" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="I2" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="J2" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="K2" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="L2" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="M2" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="N2" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="O2" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="P2" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="Q2" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="R2" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="S2" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="T2" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="U2" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="V2" t="s">
+        <v>89</v>
+      </c>
+      <c r="W2" t="s">
         <v>83</v>
       </c>
-      <c r="W2" t="s">
-        <v>77</v>
-      </c>
       <c r="X2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="Y2" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="Z2" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="AA2" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="AB2" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="AC2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="AD2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="AE2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="AF2" t="s">
-        <v>97</v>
+        <v>104</v>
       </c>
       <c r="AG2" t="s">
-        <v>102</v>
+        <v>110</v>
       </c>
       <c r="AH2" t="s">
-        <v>107</v>
+        <v>116</v>
       </c>
     </row>
     <row r="3" spans="1:34">
@@ -926,100 +956,100 @@
         <v>36</v>
       </c>
       <c r="C3" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D3" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E3" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="F3" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="G3" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="H3" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="I3" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="J3" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="K3" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="L3" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="M3" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="N3" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="O3" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="P3" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="Q3" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="R3" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="S3" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="T3" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="U3" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="V3" t="s">
+        <v>89</v>
+      </c>
+      <c r="W3" t="s">
         <v>83</v>
       </c>
-      <c r="W3" t="s">
-        <v>77</v>
-      </c>
       <c r="X3" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="Y3" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="Z3" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="AA3" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="AB3" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="AC3" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="AD3" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="AE3" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="AF3" t="s">
-        <v>98</v>
+        <v>105</v>
       </c>
       <c r="AG3" t="s">
-        <v>103</v>
+        <v>111</v>
       </c>
       <c r="AH3" t="s">
-        <v>108</v>
+        <v>117</v>
       </c>
     </row>
     <row r="4" spans="1:34">
@@ -1030,100 +1060,100 @@
         <v>37</v>
       </c>
       <c r="C4" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E4" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="F4" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="G4" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="H4" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="I4" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="J4" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="K4" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="L4" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="M4" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="N4" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="O4" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="P4" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="Q4" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="R4" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="S4" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="T4" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="U4" t="s">
+        <v>88</v>
+      </c>
+      <c r="V4" t="s">
+        <v>89</v>
+      </c>
+      <c r="W4" t="s">
+        <v>83</v>
+      </c>
+      <c r="X4" t="s">
+        <v>42</v>
+      </c>
+      <c r="Y4" t="s">
+        <v>85</v>
+      </c>
+      <c r="Z4" t="s">
+        <v>91</v>
+      </c>
+      <c r="AA4" t="s">
         <v>82</v>
       </c>
-      <c r="V4" t="s">
-        <v>83</v>
-      </c>
-      <c r="W4" t="s">
-        <v>77</v>
-      </c>
-      <c r="X4" t="s">
-        <v>41</v>
-      </c>
-      <c r="Y4" t="s">
-        <v>79</v>
-      </c>
-      <c r="Z4" t="s">
-        <v>85</v>
-      </c>
-      <c r="AA4" t="s">
-        <v>76</v>
-      </c>
       <c r="AB4" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="AC4" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="AD4" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="AE4" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="AF4" t="s">
-        <v>99</v>
+        <v>106</v>
       </c>
       <c r="AG4" t="s">
-        <v>104</v>
+        <v>112</v>
       </c>
       <c r="AH4" t="s">
-        <v>109</v>
+        <v>118</v>
       </c>
     </row>
     <row r="5" spans="1:34">
@@ -1134,100 +1164,100 @@
         <v>38</v>
       </c>
       <c r="C5" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D5" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E5" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="F5" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="G5" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="H5" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="I5" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="J5" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="K5" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="L5" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="M5" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="N5" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="O5" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="P5" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="Q5" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="R5" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="S5" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="T5" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="U5" t="s">
+        <v>88</v>
+      </c>
+      <c r="V5" t="s">
+        <v>89</v>
+      </c>
+      <c r="W5" t="s">
+        <v>83</v>
+      </c>
+      <c r="X5" t="s">
+        <v>42</v>
+      </c>
+      <c r="Y5" t="s">
+        <v>85</v>
+      </c>
+      <c r="Z5" t="s">
+        <v>91</v>
+      </c>
+      <c r="AA5" t="s">
         <v>82</v>
       </c>
-      <c r="V5" t="s">
-        <v>83</v>
-      </c>
-      <c r="W5" t="s">
-        <v>77</v>
-      </c>
-      <c r="X5" t="s">
-        <v>41</v>
-      </c>
-      <c r="Y5" t="s">
-        <v>79</v>
-      </c>
-      <c r="Z5" t="s">
-        <v>85</v>
-      </c>
-      <c r="AA5" t="s">
-        <v>76</v>
-      </c>
       <c r="AB5" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="AC5" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="AD5" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="AE5" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="AF5" t="s">
-        <v>100</v>
+        <v>107</v>
       </c>
       <c r="AG5" t="s">
-        <v>105</v>
+        <v>113</v>
       </c>
       <c r="AH5" t="s">
-        <v>109</v>
+        <v>119</v>
       </c>
     </row>
     <row r="6" spans="1:34">
@@ -1238,100 +1268,100 @@
         <v>39</v>
       </c>
       <c r="C6" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D6" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E6" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="F6" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="G6" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="H6" t="s">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="I6" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="J6" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="K6" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="L6" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="M6" t="s">
-        <v>66</v>
+        <v>76</v>
       </c>
       <c r="N6" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="O6" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="P6" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="Q6" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="R6" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="S6" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="T6" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="U6" t="s">
-        <v>81</v>
+        <v>88</v>
       </c>
       <c r="V6" t="s">
-        <v>41</v>
+        <v>89</v>
       </c>
       <c r="W6" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="X6" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="Y6" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Z6" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="AA6" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="AB6" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="AC6" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="AD6" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="AE6" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="AF6" t="s">
-        <v>101</v>
+        <v>108</v>
       </c>
       <c r="AG6" t="s">
-        <v>106</v>
+        <v>114</v>
       </c>
       <c r="AH6" t="s">
-        <v>110</v>
+        <v>118</v>
       </c>
     </row>
     <row r="7" spans="1:34">
@@ -1342,100 +1372,204 @@
         <v>40</v>
       </c>
       <c r="C7" t="s">
+        <v>42</v>
+      </c>
+      <c r="D7" t="s">
+        <v>48</v>
+      </c>
+      <c r="E7" t="s">
+        <v>55</v>
+      </c>
+      <c r="F7" t="s">
+        <v>57</v>
+      </c>
+      <c r="G7" t="s">
+        <v>58</v>
+      </c>
+      <c r="H7" t="s">
+        <v>58</v>
+      </c>
+      <c r="I7" t="s">
+        <v>64</v>
+      </c>
+      <c r="J7" t="s">
+        <v>70</v>
+      </c>
+      <c r="K7" t="s">
+        <v>71</v>
+      </c>
+      <c r="L7" t="s">
+        <v>71</v>
+      </c>
+      <c r="M7" t="s">
+        <v>71</v>
+      </c>
+      <c r="N7" t="s">
+        <v>79</v>
+      </c>
+      <c r="O7" t="s">
+        <v>80</v>
+      </c>
+      <c r="P7" t="s">
+        <v>82</v>
+      </c>
+      <c r="Q7" t="s">
+        <v>71</v>
+      </c>
+      <c r="R7" t="s">
+        <v>83</v>
+      </c>
+      <c r="S7" t="s">
+        <v>85</v>
+      </c>
+      <c r="T7" t="s">
+        <v>86</v>
+      </c>
+      <c r="U7" t="s">
+        <v>87</v>
+      </c>
+      <c r="V7" t="s">
+        <v>42</v>
+      </c>
+      <c r="W7" t="s">
+        <v>83</v>
+      </c>
+      <c r="X7" t="s">
+        <v>42</v>
+      </c>
+      <c r="Y7" t="s">
+        <v>90</v>
+      </c>
+      <c r="Z7" t="s">
+        <v>91</v>
+      </c>
+      <c r="AA7" t="s">
+        <v>92</v>
+      </c>
+      <c r="AB7" t="s">
+        <v>93</v>
+      </c>
+      <c r="AC7" t="s">
+        <v>42</v>
+      </c>
+      <c r="AD7" t="s">
+        <v>96</v>
+      </c>
+      <c r="AE7" t="s">
+        <v>102</v>
+      </c>
+      <c r="AF7" t="s">
+        <v>109</v>
+      </c>
+      <c r="AG7" t="s">
+        <v>115</v>
+      </c>
+      <c r="AH7" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="8" spans="1:34">
+      <c r="A8" t="s">
+        <v>34</v>
+      </c>
+      <c r="B8" t="s">
         <v>41</v>
       </c>
-      <c r="D7" t="s">
-        <v>47</v>
-      </c>
-      <c r="E7" t="s">
-        <v>53</v>
-      </c>
-      <c r="F7" t="s">
-        <v>54</v>
-      </c>
-      <c r="G7" t="s">
-        <v>55</v>
-      </c>
-      <c r="H7" t="s">
-        <v>55</v>
-      </c>
-      <c r="I7" t="s">
-        <v>59</v>
-      </c>
-      <c r="J7" t="s">
-        <v>66</v>
-      </c>
-      <c r="K7" t="s">
-        <v>66</v>
-      </c>
-      <c r="L7" t="s">
-        <v>66</v>
-      </c>
-      <c r="M7" t="s">
-        <v>66</v>
-      </c>
-      <c r="N7" t="s">
-        <v>71</v>
-      </c>
-      <c r="O7" t="s">
-        <v>74</v>
-      </c>
-      <c r="P7" t="s">
-        <v>76</v>
-      </c>
-      <c r="Q7" t="s">
-        <v>66</v>
-      </c>
-      <c r="R7" t="s">
+      <c r="C8" t="s">
+        <v>42</v>
+      </c>
+      <c r="D8" t="s">
+        <v>49</v>
+      </c>
+      <c r="E8" t="s">
+        <v>56</v>
+      </c>
+      <c r="F8" t="s">
+        <v>57</v>
+      </c>
+      <c r="G8" t="s">
+        <v>58</v>
+      </c>
+      <c r="H8" t="s">
+        <v>58</v>
+      </c>
+      <c r="I8" t="s">
+        <v>63</v>
+      </c>
+      <c r="J8" t="s">
+        <v>71</v>
+      </c>
+      <c r="K8" t="s">
+        <v>71</v>
+      </c>
+      <c r="L8" t="s">
+        <v>71</v>
+      </c>
+      <c r="M8" t="s">
+        <v>71</v>
+      </c>
+      <c r="N8" t="s">
         <v>77</v>
       </c>
-      <c r="S7" t="s">
-        <v>79</v>
-      </c>
-      <c r="T7" t="s">
+      <c r="O8" t="s">
         <v>80</v>
       </c>
-      <c r="U7" t="s">
-        <v>81</v>
-      </c>
-      <c r="V7" t="s">
-        <v>41</v>
-      </c>
-      <c r="W7" t="s">
-        <v>77</v>
-      </c>
-      <c r="X7" t="s">
-        <v>41</v>
-      </c>
-      <c r="Y7" t="s">
-        <v>84</v>
-      </c>
-      <c r="Z7" t="s">
+      <c r="P8" t="s">
+        <v>82</v>
+      </c>
+      <c r="Q8" t="s">
+        <v>71</v>
+      </c>
+      <c r="R8" t="s">
+        <v>83</v>
+      </c>
+      <c r="S8" t="s">
         <v>85</v>
       </c>
-      <c r="AA7" t="s">
+      <c r="T8" t="s">
         <v>86</v>
       </c>
-      <c r="AB7" t="s">
+      <c r="U8" t="s">
         <v>87</v>
       </c>
-      <c r="AC7" t="s">
-        <v>41</v>
-      </c>
-      <c r="AD7" t="s">
+      <c r="V8" t="s">
+        <v>42</v>
+      </c>
+      <c r="W8" t="s">
+        <v>83</v>
+      </c>
+      <c r="X8" t="s">
+        <v>42</v>
+      </c>
+      <c r="Y8" t="s">
+        <v>90</v>
+      </c>
+      <c r="Z8" t="s">
         <v>91</v>
       </c>
-      <c r="AE7" t="s">
-        <v>96</v>
-      </c>
-      <c r="AF7" t="s">
-        <v>91</v>
-      </c>
-      <c r="AG7" t="s">
-        <v>106</v>
-      </c>
-      <c r="AH7" t="s">
-        <v>111</v>
+      <c r="AA8" t="s">
+        <v>92</v>
+      </c>
+      <c r="AB8" t="s">
+        <v>93</v>
+      </c>
+      <c r="AC8" t="s">
+        <v>42</v>
+      </c>
+      <c r="AD8" t="s">
+        <v>97</v>
+      </c>
+      <c r="AE8" t="s">
+        <v>103</v>
+      </c>
+      <c r="AF8" t="s">
+        <v>97</v>
+      </c>
+      <c r="AG8" t="s">
+        <v>115</v>
+      </c>
+      <c r="AH8" t="s">
+        <v>121</v>
       </c>
     </row>
   </sheetData>

--- a/surgical_staging/STAGED_CRS620MI_Suppliers.xlsx
+++ b/surgical_staging/STAGED_CRS620MI_Suppliers.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="272" uniqueCount="122">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="408" uniqueCount="136">
   <si>
     <t>IDCONO</t>
   </si>
@@ -121,70 +121,106 @@
     <t>100.0</t>
   </si>
   <si>
-    <t xml:space="preserve">160118    </t>
-  </si>
-  <si>
-    <t xml:space="preserve">160231    </t>
-  </si>
-  <si>
-    <t xml:space="preserve">500970    </t>
-  </si>
-  <si>
-    <t xml:space="preserve">501013    </t>
-  </si>
-  <si>
-    <t xml:space="preserve">501023    </t>
-  </si>
-  <si>
-    <t xml:space="preserve">395056    </t>
-  </si>
-  <si>
-    <t xml:space="preserve">395453    </t>
+    <t xml:space="preserve">502125    </t>
+  </si>
+  <si>
+    <t xml:space="preserve">166993    </t>
+  </si>
+  <si>
+    <t xml:space="preserve">160047    </t>
+  </si>
+  <si>
+    <t xml:space="preserve">167602    </t>
+  </si>
+  <si>
+    <t xml:space="preserve">169833    </t>
+  </si>
+  <si>
+    <t xml:space="preserve">169912    </t>
+  </si>
+  <si>
+    <t xml:space="preserve">169920    </t>
+  </si>
+  <si>
+    <t xml:space="preserve">169944    </t>
+  </si>
+  <si>
+    <t xml:space="preserve">170580    </t>
+  </si>
+  <si>
+    <t xml:space="preserve">170590    </t>
+  </si>
+  <si>
+    <t xml:space="preserve">170592    </t>
   </si>
   <si>
     <t>0.0</t>
   </si>
   <si>
-    <t xml:space="preserve">Ampacet Canada                      </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Berg Industrial Service             </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Soarus, L.L.C.                      </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stonhard                            </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sun Chemical Corp                   </t>
-  </si>
-  <si>
-    <t xml:space="preserve">ULINE SHIPPING SUPPLIES SDERLDECV   </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Flex Films (USA), Inc.              </t>
-  </si>
-  <si>
-    <t xml:space="preserve">AMP       </t>
-  </si>
-  <si>
-    <t>BERG INDUS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SOARUS    </t>
-  </si>
-  <si>
-    <t xml:space="preserve">STONHARD  </t>
-  </si>
-  <si>
-    <t xml:space="preserve">SUN CHEM  </t>
-  </si>
-  <si>
-    <t xml:space="preserve">F         </t>
-  </si>
-  <si>
-    <t>FLEX FILMS</t>
+    <t xml:space="preserve">Ingenia Polymers                    </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Equistar Chemicals LP               </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chevron Phillips                    </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fernando Marquez                    </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Formosa Plastics Corporation, Texas </t>
+  </si>
+  <si>
+    <t xml:space="preserve">PureCycle Ohio, LLC                 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Westlake Polymers Inc               </t>
+  </si>
+  <si>
+    <t xml:space="preserve">LG Chem America, Inc                </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pinnacle Polymers LLC               </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wilk 2 Sp. z o. o                   </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Xiamen Deguan Technology Co. Ltd.   </t>
+  </si>
+  <si>
+    <t>INGENIA PO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EQUISTAR  </t>
+  </si>
+  <si>
+    <t>CHEVRON PH</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FERNANDO  </t>
+  </si>
+  <si>
+    <t>FORMOSA PL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PURECYCLE </t>
+  </si>
+  <si>
+    <t>WESTLAKE P</t>
+  </si>
+  <si>
+    <t>LG CHEM AM</t>
+  </si>
+  <si>
+    <t>PINNACLE P</t>
+  </si>
+  <si>
+    <t>WILK 2 SP.</t>
+  </si>
+  <si>
+    <t>XIAMEN DEG</t>
   </si>
   <si>
     <t>20</t>
@@ -193,193 +229,199 @@
     <t xml:space="preserve">           </t>
   </si>
   <si>
-    <t xml:space="preserve">560184790  </t>
-  </si>
-  <si>
-    <t xml:space="preserve">222761297  </t>
-  </si>
-  <si>
-    <t xml:space="preserve">36-4079419 </t>
-  </si>
-  <si>
     <t xml:space="preserve">FEDERAL ID </t>
   </si>
   <si>
     <t>GB</t>
   </si>
   <si>
-    <t>SP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(800) 265-6711  </t>
-  </si>
-  <si>
-    <t>755-2221X806KEVN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(847) 255-1211  </t>
-  </si>
-  <si>
-    <t xml:space="preserve">(770) 425-9215  </t>
-  </si>
-  <si>
-    <t xml:space="preserve">(404) 355-4131  </t>
-  </si>
-  <si>
-    <t xml:space="preserve">664 647 2045    </t>
+    <t xml:space="preserve">713-296-1500    </t>
+  </si>
+  <si>
+    <t xml:space="preserve">713-309-7781    </t>
+  </si>
+  <si>
+    <t xml:space="preserve">888-552-6789    </t>
   </si>
   <si>
     <t xml:space="preserve">                </t>
   </si>
   <si>
-    <t xml:space="preserve">806             </t>
-  </si>
-  <si>
-    <t xml:space="preserve">416-755-6022    </t>
-  </si>
-  <si>
-    <t xml:space="preserve">(847) 255-4343  </t>
-  </si>
-  <si>
-    <t xml:space="preserve">(770) 425-6215  </t>
-  </si>
-  <si>
-    <t xml:space="preserve">(404) 355-8741  </t>
+    <t xml:space="preserve">404-400-6124    </t>
+  </si>
+  <si>
+    <t xml:space="preserve">(985) 535-2000  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">800 231-4638    </t>
+  </si>
+  <si>
+    <t xml:space="preserve">713 289-4989    </t>
+  </si>
+  <si>
+    <t xml:space="preserve">713-296-1501    </t>
+  </si>
+  <si>
+    <t xml:space="preserve">713-309-4974    </t>
+  </si>
+  <si>
+    <t xml:space="preserve">(713) 754-4479  </t>
   </si>
   <si>
     <t xml:space="preserve">US </t>
   </si>
   <si>
-    <t xml:space="preserve">CA </t>
-  </si>
-  <si>
-    <t xml:space="preserve">MX </t>
+    <t xml:space="preserve">PL </t>
+  </si>
+  <si>
+    <t xml:space="preserve">CN </t>
   </si>
   <si>
     <t>YMD</t>
   </si>
   <si>
+    <t>MDY</t>
+  </si>
+  <si>
     <t>/</t>
   </si>
   <si>
+    <t xml:space="preserve">          </t>
+  </si>
+  <si>
+    <t xml:space="preserve">   </t>
+  </si>
+  <si>
+    <t xml:space="preserve">B  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">                    </t>
+  </si>
+  <si>
+    <t xml:space="preserve">*                   </t>
+  </si>
+  <si>
+    <t xml:space="preserve">4 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">  </t>
+  </si>
+  <si>
+    <t>1.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">     </t>
+  </si>
+  <si>
     <t xml:space="preserve"> </t>
   </si>
   <si>
-    <t xml:space="preserve">          </t>
-  </si>
-  <si>
-    <t xml:space="preserve">B  </t>
-  </si>
-  <si>
-    <t xml:space="preserve">   </t>
-  </si>
-  <si>
-    <t xml:space="preserve">                    </t>
-  </si>
-  <si>
-    <t xml:space="preserve">  </t>
-  </si>
-  <si>
-    <t xml:space="preserve">4 </t>
-  </si>
-  <si>
-    <t>1.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">*  </t>
-  </si>
-  <si>
-    <t xml:space="preserve">     </t>
-  </si>
-  <si>
-    <t>*</t>
-  </si>
-  <si>
     <t xml:space="preserve">      </t>
   </si>
   <si>
-    <t>20000324.0</t>
-  </si>
-  <si>
-    <t>20001121.0</t>
-  </si>
-  <si>
-    <t>20121029.0</t>
-  </si>
-  <si>
-    <t>20190312.0</t>
-  </si>
-  <si>
-    <t>115131.0</t>
-  </si>
-  <si>
-    <t>141519.0</t>
-  </si>
-  <si>
-    <t>141523.0</t>
-  </si>
-  <si>
-    <t>141524.0</t>
-  </si>
-  <si>
-    <t>163333.0</t>
-  </si>
-  <si>
-    <t>210742.0</t>
-  </si>
-  <si>
-    <t>20131104.0</t>
-  </si>
-  <si>
-    <t>20250219.0</t>
-  </si>
-  <si>
-    <t>20230814.0</t>
-  </si>
-  <si>
-    <t>20050127.0</t>
-  </si>
-  <si>
-    <t>20251204.0</t>
-  </si>
-  <si>
-    <t>20130604.0</t>
-  </si>
-  <si>
-    <t>69.0</t>
-  </si>
-  <si>
-    <t>6.0</t>
-  </si>
-  <si>
-    <t>90.0</t>
-  </si>
-  <si>
-    <t>75.0</t>
-  </si>
-  <si>
-    <t>83.0</t>
-  </si>
-  <si>
-    <t>225.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">W45METYD  </t>
-  </si>
-  <si>
-    <t xml:space="preserve">W45MEVNH  </t>
+    <t>20051206.0</t>
+  </si>
+  <si>
+    <t>20061122.0</t>
+  </si>
+  <si>
+    <t>20080729.0</t>
+  </si>
+  <si>
+    <t>20140515.0</t>
+  </si>
+  <si>
+    <t>20210527.0</t>
+  </si>
+  <si>
+    <t>20230227.0</t>
+  </si>
+  <si>
+    <t>20230424.0</t>
+  </si>
+  <si>
+    <t>20230811.0</t>
+  </si>
+  <si>
+    <t>20251003.0</t>
+  </si>
+  <si>
+    <t>20251210.0</t>
+  </si>
+  <si>
+    <t>20251219.0</t>
+  </si>
+  <si>
+    <t>163104.0</t>
+  </si>
+  <si>
+    <t>123724.0</t>
+  </si>
+  <si>
+    <t>165449.0</t>
+  </si>
+  <si>
+    <t>152343.0</t>
+  </si>
+  <si>
+    <t>142111.0</t>
+  </si>
+  <si>
+    <t>95019.0</t>
+  </si>
+  <si>
+    <t>163211.0</t>
+  </si>
+  <si>
+    <t>84941.0</t>
+  </si>
+  <si>
+    <t>131704.0</t>
+  </si>
+  <si>
+    <t>91838.0</t>
+  </si>
+  <si>
+    <t>90450.0</t>
+  </si>
+  <si>
+    <t>20120127.0</t>
+  </si>
+  <si>
+    <t>20081203.0</t>
+  </si>
+  <si>
+    <t>20101104.0</t>
+  </si>
+  <si>
+    <t>207.0</t>
+  </si>
+  <si>
+    <t>102.0</t>
+  </si>
+  <si>
+    <t>105.0</t>
+  </si>
+  <si>
+    <t>386.0</t>
+  </si>
+  <si>
+    <t>2.0</t>
   </si>
   <si>
     <t xml:space="preserve">W20ACCAE  </t>
   </si>
   <si>
-    <t xml:space="preserve">W20ACSNE  </t>
-  </si>
-  <si>
-    <t xml:space="preserve">W70MEFOR  </t>
-  </si>
-  <si>
-    <t xml:space="preserve">W70MEMSM  </t>
+    <t xml:space="preserve">W35ACMNG  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">W40MEBYS  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">W35ACNYD  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">W41MEMLB  </t>
   </si>
 </sst>
 </file>
@@ -737,7 +779,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AH8"/>
+  <dimension ref="A1:AH12"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:34">
@@ -852,100 +894,100 @@
         <v>35</v>
       </c>
       <c r="C2" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="D2" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="E2" t="s">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="F2" t="s">
-        <v>57</v>
+        <v>69</v>
       </c>
       <c r="G2" t="s">
-        <v>58</v>
+        <v>70</v>
       </c>
       <c r="H2" t="s">
-        <v>58</v>
+        <v>71</v>
       </c>
       <c r="I2" t="s">
-        <v>63</v>
+        <v>72</v>
       </c>
       <c r="J2" t="s">
-        <v>65</v>
+        <v>73</v>
       </c>
       <c r="K2" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="L2" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="M2" t="s">
-        <v>71</v>
+        <v>81</v>
       </c>
       <c r="N2" t="s">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="O2" t="s">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="P2" t="s">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="Q2" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="R2" t="s">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="S2" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="T2" t="s">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="U2" t="s">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="V2" t="s">
-        <v>89</v>
+        <v>46</v>
       </c>
       <c r="W2" t="s">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="X2" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="Y2" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="Z2" t="s">
-        <v>91</v>
+        <v>98</v>
       </c>
       <c r="AA2" t="s">
-        <v>82</v>
+        <v>99</v>
       </c>
       <c r="AB2" t="s">
-        <v>93</v>
+        <v>100</v>
       </c>
       <c r="AC2" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="AD2" t="s">
-        <v>42</v>
+        <v>101</v>
       </c>
       <c r="AE2" t="s">
-        <v>42</v>
+        <v>112</v>
       </c>
       <c r="AF2" t="s">
-        <v>104</v>
+        <v>123</v>
       </c>
       <c r="AG2" t="s">
-        <v>110</v>
+        <v>126</v>
       </c>
       <c r="AH2" t="s">
-        <v>116</v>
+        <v>131</v>
       </c>
     </row>
     <row r="3" spans="1:34">
@@ -956,100 +998,100 @@
         <v>36</v>
       </c>
       <c r="C3" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="D3" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="E3" t="s">
-        <v>51</v>
+        <v>59</v>
       </c>
       <c r="F3" t="s">
-        <v>57</v>
+        <v>69</v>
       </c>
       <c r="G3" t="s">
-        <v>58</v>
+        <v>70</v>
       </c>
       <c r="H3" t="s">
-        <v>58</v>
+        <v>70</v>
       </c>
       <c r="I3" t="s">
-        <v>63</v>
+        <v>72</v>
       </c>
       <c r="J3" t="s">
-        <v>66</v>
+        <v>74</v>
       </c>
       <c r="K3" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="L3" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="M3" t="s">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="N3" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="O3" t="s">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="P3" t="s">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="Q3" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="R3" t="s">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="S3" t="s">
-        <v>84</v>
+        <v>92</v>
       </c>
       <c r="T3" t="s">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="U3" t="s">
-        <v>87</v>
+        <v>96</v>
       </c>
       <c r="V3" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="W3" t="s">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="X3" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="Y3" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="Z3" t="s">
-        <v>91</v>
+        <v>98</v>
       </c>
       <c r="AA3" t="s">
-        <v>82</v>
+        <v>99</v>
       </c>
       <c r="AB3" t="s">
-        <v>93</v>
+        <v>100</v>
       </c>
       <c r="AC3" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="AD3" t="s">
-        <v>94</v>
+        <v>102</v>
       </c>
       <c r="AE3" t="s">
-        <v>98</v>
+        <v>113</v>
       </c>
       <c r="AF3" t="s">
-        <v>105</v>
+        <v>124</v>
       </c>
       <c r="AG3" t="s">
-        <v>111</v>
+        <v>127</v>
       </c>
       <c r="AH3" t="s">
-        <v>117</v>
+        <v>132</v>
       </c>
     </row>
     <row r="4" spans="1:34">
@@ -1060,100 +1102,100 @@
         <v>37</v>
       </c>
       <c r="C4" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="D4" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="E4" t="s">
-        <v>52</v>
+        <v>60</v>
       </c>
       <c r="F4" t="s">
-        <v>57</v>
+        <v>69</v>
       </c>
       <c r="G4" t="s">
-        <v>58</v>
+        <v>70</v>
       </c>
       <c r="H4" t="s">
-        <v>61</v>
+        <v>70</v>
       </c>
       <c r="I4" t="s">
-        <v>63</v>
+        <v>72</v>
       </c>
       <c r="J4" t="s">
-        <v>67</v>
+        <v>75</v>
       </c>
       <c r="K4" t="s">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="L4" t="s">
-        <v>71</v>
+        <v>80</v>
       </c>
       <c r="M4" t="s">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="N4" t="s">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="O4" t="s">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="P4" t="s">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="Q4" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="R4" t="s">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="S4" t="s">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="T4" t="s">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="U4" t="s">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="V4" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="W4" t="s">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="X4" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="Y4" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="Z4" t="s">
-        <v>91</v>
+        <v>98</v>
       </c>
       <c r="AA4" t="s">
-        <v>82</v>
+        <v>99</v>
       </c>
       <c r="AB4" t="s">
-        <v>93</v>
+        <v>100</v>
       </c>
       <c r="AC4" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="AD4" t="s">
-        <v>95</v>
+        <v>103</v>
       </c>
       <c r="AE4" t="s">
-        <v>99</v>
+        <v>114</v>
       </c>
       <c r="AF4" t="s">
-        <v>106</v>
+        <v>125</v>
       </c>
       <c r="AG4" t="s">
-        <v>112</v>
+        <v>128</v>
       </c>
       <c r="AH4" t="s">
-        <v>118</v>
+        <v>133</v>
       </c>
     </row>
     <row r="5" spans="1:34">
@@ -1164,100 +1206,100 @@
         <v>38</v>
       </c>
       <c r="C5" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="D5" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="E5" t="s">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="F5" t="s">
-        <v>57</v>
+        <v>69</v>
       </c>
       <c r="G5" t="s">
-        <v>59</v>
+        <v>70</v>
       </c>
       <c r="H5" t="s">
-        <v>62</v>
+        <v>70</v>
       </c>
       <c r="I5" t="s">
-        <v>63</v>
+        <v>72</v>
       </c>
       <c r="J5" t="s">
-        <v>68</v>
+        <v>76</v>
       </c>
       <c r="K5" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="L5" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="M5" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="N5" t="s">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="O5" t="s">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="P5" t="s">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="Q5" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="R5" t="s">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="S5" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="T5" t="s">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="U5" t="s">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="V5" t="s">
-        <v>89</v>
+        <v>46</v>
       </c>
       <c r="W5" t="s">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="X5" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="Y5" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="Z5" t="s">
-        <v>91</v>
+        <v>98</v>
       </c>
       <c r="AA5" t="s">
-        <v>82</v>
+        <v>99</v>
       </c>
       <c r="AB5" t="s">
-        <v>93</v>
+        <v>100</v>
       </c>
       <c r="AC5" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="AD5" t="s">
-        <v>95</v>
+        <v>104</v>
       </c>
       <c r="AE5" t="s">
-        <v>100</v>
+        <v>115</v>
       </c>
       <c r="AF5" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="AG5" t="s">
-        <v>113</v>
+        <v>129</v>
       </c>
       <c r="AH5" t="s">
-        <v>119</v>
+        <v>134</v>
       </c>
     </row>
     <row r="6" spans="1:34">
@@ -1268,100 +1310,100 @@
         <v>39</v>
       </c>
       <c r="C6" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="D6" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="E6" t="s">
-        <v>54</v>
+        <v>62</v>
       </c>
       <c r="F6" t="s">
-        <v>57</v>
+        <v>69</v>
       </c>
       <c r="G6" t="s">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="H6" t="s">
-        <v>62</v>
+        <v>70</v>
       </c>
       <c r="I6" t="s">
-        <v>63</v>
+        <v>72</v>
       </c>
       <c r="J6" t="s">
-        <v>69</v>
+        <v>76</v>
       </c>
       <c r="K6" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="L6" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="M6" t="s">
         <v>76</v>
       </c>
       <c r="N6" t="s">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="O6" t="s">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="P6" t="s">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="Q6" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="R6" t="s">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="S6" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="T6" t="s">
-        <v>86</v>
+        <v>94</v>
       </c>
       <c r="U6" t="s">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="V6" t="s">
-        <v>89</v>
+        <v>46</v>
       </c>
       <c r="W6" t="s">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="X6" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="Y6" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="Z6" t="s">
-        <v>91</v>
+        <v>98</v>
       </c>
       <c r="AA6" t="s">
-        <v>82</v>
+        <v>99</v>
       </c>
       <c r="AB6" t="s">
-        <v>93</v>
+        <v>100</v>
       </c>
       <c r="AC6" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="AD6" t="s">
-        <v>95</v>
+        <v>105</v>
       </c>
       <c r="AE6" t="s">
-        <v>101</v>
+        <v>116</v>
       </c>
       <c r="AF6" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="AG6" t="s">
-        <v>114</v>
+        <v>130</v>
       </c>
       <c r="AH6" t="s">
-        <v>118</v>
+        <v>135</v>
       </c>
     </row>
     <row r="7" spans="1:34">
@@ -1372,100 +1414,100 @@
         <v>40</v>
       </c>
       <c r="C7" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="D7" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="E7" t="s">
-        <v>55</v>
+        <v>63</v>
       </c>
       <c r="F7" t="s">
-        <v>57</v>
+        <v>69</v>
       </c>
       <c r="G7" t="s">
-        <v>58</v>
+        <v>70</v>
       </c>
       <c r="H7" t="s">
-        <v>58</v>
+        <v>70</v>
       </c>
       <c r="I7" t="s">
-        <v>64</v>
+        <v>72</v>
       </c>
       <c r="J7" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="K7" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="L7" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="M7" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="N7" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="O7" t="s">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="P7" t="s">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="Q7" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="R7" t="s">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="S7" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="T7" t="s">
-        <v>86</v>
+        <v>94</v>
       </c>
       <c r="U7" t="s">
-        <v>87</v>
+        <v>96</v>
       </c>
       <c r="V7" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="W7" t="s">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="X7" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="Y7" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="Z7" t="s">
-        <v>91</v>
+        <v>98</v>
       </c>
       <c r="AA7" t="s">
-        <v>92</v>
+        <v>99</v>
       </c>
       <c r="AB7" t="s">
-        <v>93</v>
+        <v>100</v>
       </c>
       <c r="AC7" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="AD7" t="s">
-        <v>96</v>
+        <v>106</v>
       </c>
       <c r="AE7" t="s">
-        <v>102</v>
+        <v>117</v>
       </c>
       <c r="AF7" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="AG7" t="s">
-        <v>115</v>
+        <v>130</v>
       </c>
       <c r="AH7" t="s">
-        <v>120</v>
+        <v>135</v>
       </c>
     </row>
     <row r="8" spans="1:34">
@@ -1476,100 +1518,516 @@
         <v>41</v>
       </c>
       <c r="C8" t="s">
+        <v>46</v>
+      </c>
+      <c r="D8" t="s">
+        <v>53</v>
+      </c>
+      <c r="E8" t="s">
+        <v>64</v>
+      </c>
+      <c r="F8" t="s">
+        <v>69</v>
+      </c>
+      <c r="G8" t="s">
+        <v>70</v>
+      </c>
+      <c r="H8" t="s">
+        <v>70</v>
+      </c>
+      <c r="I8" t="s">
+        <v>72</v>
+      </c>
+      <c r="J8" t="s">
+        <v>76</v>
+      </c>
+      <c r="K8" t="s">
+        <v>76</v>
+      </c>
+      <c r="L8" t="s">
+        <v>76</v>
+      </c>
+      <c r="M8" t="s">
+        <v>76</v>
+      </c>
+      <c r="N8" t="s">
+        <v>84</v>
+      </c>
+      <c r="O8" t="s">
+        <v>87</v>
+      </c>
+      <c r="P8" t="s">
+        <v>89</v>
+      </c>
+      <c r="Q8" t="s">
+        <v>76</v>
+      </c>
+      <c r="R8" t="s">
+        <v>90</v>
+      </c>
+      <c r="S8" t="s">
+        <v>91</v>
+      </c>
+      <c r="T8" t="s">
+        <v>94</v>
+      </c>
+      <c r="U8" t="s">
+        <v>96</v>
+      </c>
+      <c r="V8" t="s">
+        <v>46</v>
+      </c>
+      <c r="W8" t="s">
+        <v>90</v>
+      </c>
+      <c r="X8" t="s">
+        <v>46</v>
+      </c>
+      <c r="Y8" t="s">
+        <v>91</v>
+      </c>
+      <c r="Z8" t="s">
+        <v>98</v>
+      </c>
+      <c r="AA8" t="s">
+        <v>99</v>
+      </c>
+      <c r="AB8" t="s">
+        <v>100</v>
+      </c>
+      <c r="AC8" t="s">
+        <v>46</v>
+      </c>
+      <c r="AD8" t="s">
+        <v>107</v>
+      </c>
+      <c r="AE8" t="s">
+        <v>118</v>
+      </c>
+      <c r="AF8" t="s">
+        <v>107</v>
+      </c>
+      <c r="AG8" t="s">
+        <v>130</v>
+      </c>
+      <c r="AH8" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="9" spans="1:34">
+      <c r="A9" t="s">
+        <v>34</v>
+      </c>
+      <c r="B9" t="s">
         <v>42</v>
       </c>
-      <c r="D8" t="s">
-        <v>49</v>
-      </c>
-      <c r="E8" t="s">
+      <c r="C9" t="s">
+        <v>46</v>
+      </c>
+      <c r="D9" t="s">
+        <v>54</v>
+      </c>
+      <c r="E9" t="s">
+        <v>65</v>
+      </c>
+      <c r="F9" t="s">
+        <v>69</v>
+      </c>
+      <c r="G9" t="s">
+        <v>70</v>
+      </c>
+      <c r="H9" t="s">
+        <v>70</v>
+      </c>
+      <c r="I9" t="s">
+        <v>72</v>
+      </c>
+      <c r="J9" t="s">
+        <v>77</v>
+      </c>
+      <c r="K9" t="s">
+        <v>76</v>
+      </c>
+      <c r="L9" t="s">
+        <v>76</v>
+      </c>
+      <c r="M9" t="s">
+        <v>76</v>
+      </c>
+      <c r="N9" t="s">
+        <v>84</v>
+      </c>
+      <c r="O9" t="s">
+        <v>87</v>
+      </c>
+      <c r="P9" t="s">
+        <v>89</v>
+      </c>
+      <c r="Q9" t="s">
+        <v>76</v>
+      </c>
+      <c r="R9" t="s">
+        <v>90</v>
+      </c>
+      <c r="S9" t="s">
+        <v>91</v>
+      </c>
+      <c r="T9" t="s">
+        <v>94</v>
+      </c>
+      <c r="U9" t="s">
+        <v>96</v>
+      </c>
+      <c r="V9" t="s">
+        <v>46</v>
+      </c>
+      <c r="W9" t="s">
+        <v>90</v>
+      </c>
+      <c r="X9" t="s">
+        <v>46</v>
+      </c>
+      <c r="Y9" t="s">
+        <v>91</v>
+      </c>
+      <c r="Z9" t="s">
+        <v>98</v>
+      </c>
+      <c r="AA9" t="s">
+        <v>99</v>
+      </c>
+      <c r="AB9" t="s">
+        <v>100</v>
+      </c>
+      <c r="AC9" t="s">
+        <v>46</v>
+      </c>
+      <c r="AD9" t="s">
+        <v>108</v>
+      </c>
+      <c r="AE9" t="s">
+        <v>119</v>
+      </c>
+      <c r="AF9" t="s">
+        <v>108</v>
+      </c>
+      <c r="AG9" t="s">
+        <v>130</v>
+      </c>
+      <c r="AH9" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="10" spans="1:34">
+      <c r="A10" t="s">
+        <v>34</v>
+      </c>
+      <c r="B10" t="s">
+        <v>43</v>
+      </c>
+      <c r="C10" t="s">
+        <v>46</v>
+      </c>
+      <c r="D10" t="s">
+        <v>55</v>
+      </c>
+      <c r="E10" t="s">
+        <v>66</v>
+      </c>
+      <c r="F10" t="s">
+        <v>69</v>
+      </c>
+      <c r="G10" t="s">
+        <v>70</v>
+      </c>
+      <c r="H10" t="s">
+        <v>70</v>
+      </c>
+      <c r="I10" t="s">
+        <v>72</v>
+      </c>
+      <c r="J10" t="s">
+        <v>78</v>
+      </c>
+      <c r="K10" t="s">
+        <v>76</v>
+      </c>
+      <c r="L10" t="s">
+        <v>76</v>
+      </c>
+      <c r="M10" t="s">
+        <v>76</v>
+      </c>
+      <c r="N10" t="s">
+        <v>84</v>
+      </c>
+      <c r="O10" t="s">
+        <v>87</v>
+      </c>
+      <c r="P10" t="s">
+        <v>89</v>
+      </c>
+      <c r="Q10" t="s">
+        <v>76</v>
+      </c>
+      <c r="R10" t="s">
+        <v>90</v>
+      </c>
+      <c r="S10" t="s">
+        <v>91</v>
+      </c>
+      <c r="T10" t="s">
+        <v>94</v>
+      </c>
+      <c r="U10" t="s">
+        <v>96</v>
+      </c>
+      <c r="V10" t="s">
+        <v>46</v>
+      </c>
+      <c r="W10" t="s">
+        <v>90</v>
+      </c>
+      <c r="X10" t="s">
+        <v>46</v>
+      </c>
+      <c r="Y10" t="s">
+        <v>91</v>
+      </c>
+      <c r="Z10" t="s">
+        <v>98</v>
+      </c>
+      <c r="AA10" t="s">
+        <v>99</v>
+      </c>
+      <c r="AB10" t="s">
+        <v>100</v>
+      </c>
+      <c r="AC10" t="s">
+        <v>46</v>
+      </c>
+      <c r="AD10" t="s">
+        <v>109</v>
+      </c>
+      <c r="AE10" t="s">
+        <v>120</v>
+      </c>
+      <c r="AF10" t="s">
+        <v>109</v>
+      </c>
+      <c r="AG10" t="s">
+        <v>130</v>
+      </c>
+      <c r="AH10" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="11" spans="1:34">
+      <c r="A11" t="s">
+        <v>34</v>
+      </c>
+      <c r="B11" t="s">
+        <v>44</v>
+      </c>
+      <c r="C11" t="s">
+        <v>46</v>
+      </c>
+      <c r="D11" t="s">
         <v>56</v>
       </c>
-      <c r="F8" t="s">
+      <c r="E11" t="s">
+        <v>67</v>
+      </c>
+      <c r="F11" t="s">
+        <v>69</v>
+      </c>
+      <c r="G11" t="s">
+        <v>70</v>
+      </c>
+      <c r="H11" t="s">
+        <v>70</v>
+      </c>
+      <c r="I11" t="s">
+        <v>72</v>
+      </c>
+      <c r="J11" t="s">
+        <v>76</v>
+      </c>
+      <c r="K11" t="s">
+        <v>76</v>
+      </c>
+      <c r="L11" t="s">
+        <v>76</v>
+      </c>
+      <c r="M11" t="s">
+        <v>76</v>
+      </c>
+      <c r="N11" t="s">
+        <v>85</v>
+      </c>
+      <c r="O11" t="s">
+        <v>87</v>
+      </c>
+      <c r="P11" t="s">
+        <v>89</v>
+      </c>
+      <c r="Q11" t="s">
+        <v>76</v>
+      </c>
+      <c r="R11" t="s">
+        <v>90</v>
+      </c>
+      <c r="S11" t="s">
+        <v>91</v>
+      </c>
+      <c r="T11" t="s">
+        <v>94</v>
+      </c>
+      <c r="U11" t="s">
+        <v>96</v>
+      </c>
+      <c r="V11" t="s">
+        <v>46</v>
+      </c>
+      <c r="W11" t="s">
+        <v>90</v>
+      </c>
+      <c r="X11" t="s">
+        <v>46</v>
+      </c>
+      <c r="Y11" t="s">
+        <v>91</v>
+      </c>
+      <c r="Z11" t="s">
+        <v>98</v>
+      </c>
+      <c r="AA11" t="s">
+        <v>99</v>
+      </c>
+      <c r="AB11" t="s">
+        <v>100</v>
+      </c>
+      <c r="AC11" t="s">
+        <v>46</v>
+      </c>
+      <c r="AD11" t="s">
+        <v>110</v>
+      </c>
+      <c r="AE11" t="s">
+        <v>121</v>
+      </c>
+      <c r="AF11" t="s">
+        <v>110</v>
+      </c>
+      <c r="AG11" t="s">
+        <v>130</v>
+      </c>
+      <c r="AH11" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="12" spans="1:34">
+      <c r="A12" t="s">
+        <v>34</v>
+      </c>
+      <c r="B12" t="s">
+        <v>45</v>
+      </c>
+      <c r="C12" t="s">
+        <v>46</v>
+      </c>
+      <c r="D12" t="s">
         <v>57</v>
       </c>
-      <c r="G8" t="s">
-        <v>58</v>
-      </c>
-      <c r="H8" t="s">
-        <v>58</v>
-      </c>
-      <c r="I8" t="s">
-        <v>63</v>
-      </c>
-      <c r="J8" t="s">
-        <v>71</v>
-      </c>
-      <c r="K8" t="s">
-        <v>71</v>
-      </c>
-      <c r="L8" t="s">
-        <v>71</v>
-      </c>
-      <c r="M8" t="s">
-        <v>71</v>
-      </c>
-      <c r="N8" t="s">
-        <v>77</v>
-      </c>
-      <c r="O8" t="s">
-        <v>80</v>
-      </c>
-      <c r="P8" t="s">
-        <v>82</v>
-      </c>
-      <c r="Q8" t="s">
-        <v>71</v>
-      </c>
-      <c r="R8" t="s">
-        <v>83</v>
-      </c>
-      <c r="S8" t="s">
-        <v>85</v>
-      </c>
-      <c r="T8" t="s">
+      <c r="E12" t="s">
+        <v>68</v>
+      </c>
+      <c r="F12" t="s">
+        <v>69</v>
+      </c>
+      <c r="G12" t="s">
+        <v>70</v>
+      </c>
+      <c r="H12" t="s">
+        <v>70</v>
+      </c>
+      <c r="I12" t="s">
+        <v>72</v>
+      </c>
+      <c r="J12" t="s">
+        <v>76</v>
+      </c>
+      <c r="K12" t="s">
+        <v>76</v>
+      </c>
+      <c r="L12" t="s">
+        <v>76</v>
+      </c>
+      <c r="M12" t="s">
+        <v>76</v>
+      </c>
+      <c r="N12" t="s">
         <v>86</v>
       </c>
-      <c r="U8" t="s">
+      <c r="O12" t="s">
         <v>87</v>
       </c>
-      <c r="V8" t="s">
-        <v>42</v>
-      </c>
-      <c r="W8" t="s">
-        <v>83</v>
-      </c>
-      <c r="X8" t="s">
-        <v>42</v>
-      </c>
-      <c r="Y8" t="s">
-        <v>90</v>
-      </c>
-      <c r="Z8" t="s">
+      <c r="P12" t="s">
+        <v>89</v>
+      </c>
+      <c r="Q12" t="s">
+        <v>76</v>
+      </c>
+      <c r="R12" t="s">
+        <v>90</v>
+      </c>
+      <c r="S12" t="s">
         <v>91</v>
       </c>
-      <c r="AA8" t="s">
-        <v>92</v>
-      </c>
-      <c r="AB8" t="s">
-        <v>93</v>
-      </c>
-      <c r="AC8" t="s">
-        <v>42</v>
-      </c>
-      <c r="AD8" t="s">
-        <v>97</v>
-      </c>
-      <c r="AE8" t="s">
-        <v>103</v>
-      </c>
-      <c r="AF8" t="s">
-        <v>97</v>
-      </c>
-      <c r="AG8" t="s">
-        <v>115</v>
-      </c>
-      <c r="AH8" t="s">
-        <v>121</v>
+      <c r="T12" t="s">
+        <v>94</v>
+      </c>
+      <c r="U12" t="s">
+        <v>96</v>
+      </c>
+      <c r="V12" t="s">
+        <v>46</v>
+      </c>
+      <c r="W12" t="s">
+        <v>90</v>
+      </c>
+      <c r="X12" t="s">
+        <v>46</v>
+      </c>
+      <c r="Y12" t="s">
+        <v>91</v>
+      </c>
+      <c r="Z12" t="s">
+        <v>98</v>
+      </c>
+      <c r="AA12" t="s">
+        <v>99</v>
+      </c>
+      <c r="AB12" t="s">
+        <v>100</v>
+      </c>
+      <c r="AC12" t="s">
+        <v>46</v>
+      </c>
+      <c r="AD12" t="s">
+        <v>111</v>
+      </c>
+      <c r="AE12" t="s">
+        <v>122</v>
+      </c>
+      <c r="AF12" t="s">
+        <v>111</v>
+      </c>
+      <c r="AG12" t="s">
+        <v>130</v>
+      </c>
+      <c r="AH12" t="s">
+        <v>135</v>
       </c>
     </row>
   </sheetData>

--- a/surgical_staging/STAGED_CRS620MI_Suppliers.xlsx
+++ b/surgical_staging/STAGED_CRS620MI_Suppliers.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="340" uniqueCount="144">
   <si>
     <t>IDCONO</t>
   </si>
@@ -121,15 +121,84 @@
     <t>100.0</t>
   </si>
   <si>
+    <t xml:space="preserve">500003    </t>
+  </si>
+  <si>
+    <t xml:space="preserve">376047    </t>
+  </si>
+  <si>
+    <t xml:space="preserve">136036    </t>
+  </si>
+  <si>
+    <t xml:space="preserve">140376    </t>
+  </si>
+  <si>
+    <t xml:space="preserve">502125    </t>
+  </si>
+  <si>
+    <t xml:space="preserve">137652    </t>
+  </si>
+  <si>
+    <t xml:space="preserve">379811    </t>
+  </si>
+  <si>
+    <t xml:space="preserve">379886    </t>
+  </si>
+  <si>
     <t xml:space="preserve">159392    </t>
   </si>
   <si>
     <t>0.0</t>
   </si>
   <si>
+    <t>5.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ampacet Corporation                 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dow Chemical Company                </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dow Chemical Canada ULC             </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Soarus L.L.C.                       </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ingenia Polymers                    </t>
+  </si>
+  <si>
+    <t xml:space="preserve">International Trade Solutions       </t>
+  </si>
+  <si>
+    <t xml:space="preserve">SK Primacor Americas LLC            </t>
+  </si>
+  <si>
     <t xml:space="preserve">National Research Council Canada    </t>
   </si>
   <si>
+    <t xml:space="preserve">AMPACET   </t>
+  </si>
+  <si>
+    <t xml:space="preserve">DOW       </t>
+  </si>
+  <si>
+    <t>DOW CHEMIC</t>
+  </si>
+  <si>
+    <t>SOARUS LLC</t>
+  </si>
+  <si>
+    <t>INGENIA PO</t>
+  </si>
+  <si>
+    <t>INTERNATIO</t>
+  </si>
+  <si>
+    <t>SK PRIMACO</t>
+  </si>
+  <si>
     <t>NATIONAL R</t>
   </si>
   <si>
@@ -139,12 +208,72 @@
     <t xml:space="preserve">           </t>
   </si>
   <si>
+    <t xml:space="preserve">FEDERAL ID </t>
+  </si>
+  <si>
     <t>GB</t>
   </si>
   <si>
+    <t xml:space="preserve">(888) 333-7604  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">800-232-2436    </t>
+  </si>
+  <si>
+    <t xml:space="preserve">(800) 232-2436  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">(847) 255-1211  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">713-296-1500    </t>
+  </si>
+  <si>
+    <t xml:space="preserve">(701) 738-2540  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">(847) 253-1285  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">713-395-7793    </t>
+  </si>
+  <si>
     <t xml:space="preserve">                </t>
   </si>
   <si>
+    <t xml:space="preserve">(800) 809-8077  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">(888) 369-2228  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">EXT: 10         </t>
+  </si>
+  <si>
+    <t xml:space="preserve">(914) 631-7278  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">989-832-1291    </t>
+  </si>
+  <si>
+    <t xml:space="preserve">(989) 633-5637  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">(847) 255-4343  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">713-296-1501    </t>
+  </si>
+  <si>
+    <t xml:space="preserve">(701) 738-2380  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">713-850-0019    </t>
+  </si>
+  <si>
+    <t xml:space="preserve">US </t>
+  </si>
+  <si>
     <t xml:space="preserve">CA </t>
   </si>
   <si>
@@ -154,6 +283,12 @@
     <t>/</t>
   </si>
   <si>
+    <t xml:space="preserve"> </t>
+  </si>
+  <si>
+    <t xml:space="preserve">101474419RT0001 </t>
+  </si>
+  <si>
     <t xml:space="preserve">          </t>
   </si>
   <si>
@@ -163,28 +298,151 @@
     <t xml:space="preserve">                    </t>
   </si>
   <si>
+    <t xml:space="preserve">4 </t>
+  </si>
+  <si>
     <t xml:space="preserve">  </t>
   </si>
   <si>
+    <t>1.0</t>
+  </si>
+  <si>
     <t xml:space="preserve">     </t>
   </si>
   <si>
-    <t xml:space="preserve"> </t>
-  </si>
-  <si>
     <t xml:space="preserve">      </t>
   </si>
   <si>
+    <t>93829.0</t>
+  </si>
+  <si>
+    <t>20069.0</t>
+  </si>
+  <si>
+    <t>130615.0</t>
+  </si>
+  <si>
+    <t>447695.0</t>
+  </si>
+  <si>
+    <t>470127.0</t>
+  </si>
+  <si>
+    <t>20000912.0</t>
+  </si>
+  <si>
+    <t>20011217.0</t>
+  </si>
+  <si>
+    <t>20021121.0</t>
+  </si>
+  <si>
+    <t>20051206.0</t>
+  </si>
+  <si>
+    <t>20081106.0</t>
+  </si>
+  <si>
+    <t>20170404.0</t>
+  </si>
+  <si>
+    <t>20171012.0</t>
+  </si>
+  <si>
     <t>20201203.0</t>
   </si>
   <si>
+    <t>95432.0</t>
+  </si>
+  <si>
+    <t>102918.0</t>
+  </si>
+  <si>
+    <t>184843.0</t>
+  </si>
+  <si>
+    <t>184848.0</t>
+  </si>
+  <si>
+    <t>163104.0</t>
+  </si>
+  <si>
+    <t>112129.0</t>
+  </si>
+  <si>
+    <t>115427.0</t>
+  </si>
+  <si>
+    <t>143609.0</t>
+  </si>
+  <si>
     <t>93623.0</t>
   </si>
   <si>
+    <t>20180720.0</t>
+  </si>
+  <si>
+    <t>20240514.0</t>
+  </si>
+  <si>
+    <t>20210511.0</t>
+  </si>
+  <si>
+    <t>20140611.0</t>
+  </si>
+  <si>
+    <t>20120127.0</t>
+  </si>
+  <si>
+    <t>20250428.0</t>
+  </si>
+  <si>
+    <t>20230810.0</t>
+  </si>
+  <si>
+    <t>20240606.0</t>
+  </si>
+  <si>
     <t>20260331.0</t>
   </si>
   <si>
+    <t>109.0</t>
+  </si>
+  <si>
+    <t>168.0</t>
+  </si>
+  <si>
+    <t>15.0</t>
+  </si>
+  <si>
+    <t>207.0</t>
+  </si>
+  <si>
+    <t>21.0</t>
+  </si>
+  <si>
+    <t>10.0</t>
+  </si>
+  <si>
+    <t>176.0</t>
+  </si>
+  <si>
     <t>20.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">W20PUROC  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">W25ADTRJ  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">W15ACJRW  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">W15PUDAH  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">W20ACCAE  </t>
   </si>
   <si>
     <t xml:space="preserve">W15ACRAF  </t>
@@ -545,7 +803,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AH2"/>
+  <dimension ref="A1:AH10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:34">
@@ -660,100 +918,932 @@
         <v>35</v>
       </c>
       <c r="C2" t="s">
+        <v>44</v>
+      </c>
+      <c r="D2" t="s">
+        <v>46</v>
+      </c>
+      <c r="E2" t="s">
+        <v>54</v>
+      </c>
+      <c r="F2" t="s">
+        <v>62</v>
+      </c>
+      <c r="G2" t="s">
+        <v>63</v>
+      </c>
+      <c r="H2" t="s">
+        <v>64</v>
+      </c>
+      <c r="I2" t="s">
+        <v>65</v>
+      </c>
+      <c r="J2" t="s">
+        <v>66</v>
+      </c>
+      <c r="K2" t="s">
+        <v>75</v>
+      </c>
+      <c r="L2" t="s">
+        <v>74</v>
+      </c>
+      <c r="M2" t="s">
+        <v>78</v>
+      </c>
+      <c r="N2" t="s">
+        <v>85</v>
+      </c>
+      <c r="O2" t="s">
+        <v>87</v>
+      </c>
+      <c r="P2" t="s">
+        <v>88</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>74</v>
+      </c>
+      <c r="R2" t="s">
+        <v>91</v>
+      </c>
+      <c r="S2" t="s">
+        <v>92</v>
+      </c>
+      <c r="T2" t="s">
+        <v>93</v>
+      </c>
+      <c r="U2" t="s">
+        <v>94</v>
+      </c>
+      <c r="V2" t="s">
+        <v>96</v>
+      </c>
+      <c r="W2" t="s">
+        <v>91</v>
+      </c>
+      <c r="X2" t="s">
+        <v>44</v>
+      </c>
+      <c r="Y2" t="s">
+        <v>92</v>
+      </c>
+      <c r="Z2" t="s">
+        <v>97</v>
+      </c>
+      <c r="AA2" t="s">
+        <v>89</v>
+      </c>
+      <c r="AB2" t="s">
+        <v>98</v>
+      </c>
+      <c r="AC2" t="s">
+        <v>44</v>
+      </c>
+      <c r="AD2" t="s">
+        <v>104</v>
+      </c>
+      <c r="AE2" t="s">
+        <v>112</v>
+      </c>
+      <c r="AF2" t="s">
+        <v>121</v>
+      </c>
+      <c r="AG2" t="s">
+        <v>130</v>
+      </c>
+      <c r="AH2" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="3" spans="1:34">
+      <c r="A3" t="s">
+        <v>34</v>
+      </c>
+      <c r="B3" t="s">
         <v>36</v>
       </c>
-      <c r="D2" t="s">
+      <c r="C3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D3" t="s">
+        <v>47</v>
+      </c>
+      <c r="E3" t="s">
+        <v>55</v>
+      </c>
+      <c r="F3" t="s">
+        <v>62</v>
+      </c>
+      <c r="G3" t="s">
+        <v>63</v>
+      </c>
+      <c r="H3" t="s">
+        <v>63</v>
+      </c>
+      <c r="I3" t="s">
+        <v>65</v>
+      </c>
+      <c r="J3" t="s">
+        <v>67</v>
+      </c>
+      <c r="K3" t="s">
+        <v>74</v>
+      </c>
+      <c r="L3" t="s">
+        <v>74</v>
+      </c>
+      <c r="M3" t="s">
+        <v>79</v>
+      </c>
+      <c r="N3" t="s">
+        <v>85</v>
+      </c>
+      <c r="O3" t="s">
+        <v>87</v>
+      </c>
+      <c r="P3" t="s">
+        <v>89</v>
+      </c>
+      <c r="Q3" t="s">
+        <v>74</v>
+      </c>
+      <c r="R3" t="s">
+        <v>91</v>
+      </c>
+      <c r="S3" t="s">
+        <v>92</v>
+      </c>
+      <c r="T3" t="s">
+        <v>93</v>
+      </c>
+      <c r="U3" t="s">
+        <v>95</v>
+      </c>
+      <c r="V3" t="s">
+        <v>44</v>
+      </c>
+      <c r="W3" t="s">
+        <v>91</v>
+      </c>
+      <c r="X3" t="s">
+        <v>44</v>
+      </c>
+      <c r="Y3" t="s">
+        <v>92</v>
+      </c>
+      <c r="Z3" t="s">
+        <v>97</v>
+      </c>
+      <c r="AA3" t="s">
+        <v>89</v>
+      </c>
+      <c r="AB3" t="s">
+        <v>98</v>
+      </c>
+      <c r="AC3" t="s">
+        <v>99</v>
+      </c>
+      <c r="AD3" t="s">
+        <v>105</v>
+      </c>
+      <c r="AE3" t="s">
+        <v>113</v>
+      </c>
+      <c r="AF3" t="s">
+        <v>122</v>
+      </c>
+      <c r="AG3" t="s">
+        <v>131</v>
+      </c>
+      <c r="AH3" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="4" spans="1:34">
+      <c r="A4" t="s">
+        <v>34</v>
+      </c>
+      <c r="B4" t="s">
         <v>37</v>
       </c>
-      <c r="E2" t="s">
+      <c r="C4" t="s">
+        <v>44</v>
+      </c>
+      <c r="D4" t="s">
+        <v>48</v>
+      </c>
+      <c r="E4" t="s">
+        <v>56</v>
+      </c>
+      <c r="F4" t="s">
+        <v>62</v>
+      </c>
+      <c r="G4" t="s">
+        <v>63</v>
+      </c>
+      <c r="H4" t="s">
+        <v>63</v>
+      </c>
+      <c r="I4" t="s">
+        <v>65</v>
+      </c>
+      <c r="J4" t="s">
+        <v>68</v>
+      </c>
+      <c r="K4" t="s">
+        <v>76</v>
+      </c>
+      <c r="L4" t="s">
+        <v>74</v>
+      </c>
+      <c r="M4" t="s">
+        <v>80</v>
+      </c>
+      <c r="N4" t="s">
+        <v>86</v>
+      </c>
+      <c r="O4" t="s">
+        <v>87</v>
+      </c>
+      <c r="P4" t="s">
+        <v>88</v>
+      </c>
+      <c r="Q4" t="s">
+        <v>90</v>
+      </c>
+      <c r="R4" t="s">
+        <v>91</v>
+      </c>
+      <c r="S4" t="s">
+        <v>92</v>
+      </c>
+      <c r="T4" t="s">
+        <v>93</v>
+      </c>
+      <c r="U4" t="s">
+        <v>95</v>
+      </c>
+      <c r="V4" t="s">
+        <v>44</v>
+      </c>
+      <c r="W4" t="s">
+        <v>91</v>
+      </c>
+      <c r="X4" t="s">
+        <v>44</v>
+      </c>
+      <c r="Y4" t="s">
+        <v>92</v>
+      </c>
+      <c r="Z4" t="s">
+        <v>97</v>
+      </c>
+      <c r="AA4" t="s">
+        <v>89</v>
+      </c>
+      <c r="AB4" t="s">
+        <v>98</v>
+      </c>
+      <c r="AC4" t="s">
+        <v>100</v>
+      </c>
+      <c r="AD4" t="s">
+        <v>106</v>
+      </c>
+      <c r="AE4" t="s">
+        <v>114</v>
+      </c>
+      <c r="AF4" t="s">
+        <v>123</v>
+      </c>
+      <c r="AG4" t="s">
+        <v>132</v>
+      </c>
+      <c r="AH4" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="5" spans="1:34">
+      <c r="A5" t="s">
+        <v>34</v>
+      </c>
+      <c r="B5" t="s">
         <v>38</v>
       </c>
-      <c r="F2" t="s">
+      <c r="C5" t="s">
+        <v>44</v>
+      </c>
+      <c r="D5" t="s">
+        <v>49</v>
+      </c>
+      <c r="E5" t="s">
+        <v>57</v>
+      </c>
+      <c r="F5" t="s">
+        <v>62</v>
+      </c>
+      <c r="G5" t="s">
+        <v>63</v>
+      </c>
+      <c r="H5" t="s">
+        <v>63</v>
+      </c>
+      <c r="I5" t="s">
+        <v>65</v>
+      </c>
+      <c r="J5" t="s">
+        <v>69</v>
+      </c>
+      <c r="K5" t="s">
+        <v>77</v>
+      </c>
+      <c r="L5" t="s">
+        <v>74</v>
+      </c>
+      <c r="M5" t="s">
+        <v>81</v>
+      </c>
+      <c r="N5" t="s">
+        <v>85</v>
+      </c>
+      <c r="O5" t="s">
+        <v>87</v>
+      </c>
+      <c r="P5" t="s">
+        <v>88</v>
+      </c>
+      <c r="Q5" t="s">
+        <v>74</v>
+      </c>
+      <c r="R5" t="s">
+        <v>91</v>
+      </c>
+      <c r="S5" t="s">
+        <v>92</v>
+      </c>
+      <c r="T5" t="s">
+        <v>93</v>
+      </c>
+      <c r="U5" t="s">
+        <v>95</v>
+      </c>
+      <c r="V5" t="s">
+        <v>44</v>
+      </c>
+      <c r="W5" t="s">
+        <v>91</v>
+      </c>
+      <c r="X5" t="s">
+        <v>44</v>
+      </c>
+      <c r="Y5" t="s">
+        <v>92</v>
+      </c>
+      <c r="Z5" t="s">
+        <v>97</v>
+      </c>
+      <c r="AA5" t="s">
+        <v>89</v>
+      </c>
+      <c r="AB5" t="s">
+        <v>98</v>
+      </c>
+      <c r="AC5" t="s">
+        <v>44</v>
+      </c>
+      <c r="AD5" t="s">
+        <v>106</v>
+      </c>
+      <c r="AE5" t="s">
+        <v>115</v>
+      </c>
+      <c r="AF5" t="s">
+        <v>124</v>
+      </c>
+      <c r="AG5" t="s">
+        <v>45</v>
+      </c>
+      <c r="AH5" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="6" spans="1:34">
+      <c r="A6" t="s">
+        <v>34</v>
+      </c>
+      <c r="B6" t="s">
         <v>39</v>
       </c>
-      <c r="G2" t="s">
+      <c r="C6" t="s">
+        <v>44</v>
+      </c>
+      <c r="D6" t="s">
+        <v>50</v>
+      </c>
+      <c r="E6" t="s">
+        <v>58</v>
+      </c>
+      <c r="F6" t="s">
+        <v>62</v>
+      </c>
+      <c r="G6" t="s">
+        <v>63</v>
+      </c>
+      <c r="H6" t="s">
+        <v>64</v>
+      </c>
+      <c r="I6" t="s">
+        <v>65</v>
+      </c>
+      <c r="J6" t="s">
+        <v>70</v>
+      </c>
+      <c r="K6" t="s">
+        <v>74</v>
+      </c>
+      <c r="L6" t="s">
+        <v>74</v>
+      </c>
+      <c r="M6" t="s">
+        <v>82</v>
+      </c>
+      <c r="N6" t="s">
+        <v>85</v>
+      </c>
+      <c r="O6" t="s">
+        <v>87</v>
+      </c>
+      <c r="P6" t="s">
+        <v>88</v>
+      </c>
+      <c r="Q6" t="s">
+        <v>74</v>
+      </c>
+      <c r="R6" t="s">
+        <v>91</v>
+      </c>
+      <c r="S6" t="s">
+        <v>92</v>
+      </c>
+      <c r="T6" t="s">
+        <v>93</v>
+      </c>
+      <c r="U6" t="s">
+        <v>94</v>
+      </c>
+      <c r="V6" t="s">
+        <v>44</v>
+      </c>
+      <c r="W6" t="s">
+        <v>91</v>
+      </c>
+      <c r="X6" t="s">
+        <v>44</v>
+      </c>
+      <c r="Y6" t="s">
+        <v>92</v>
+      </c>
+      <c r="Z6" t="s">
+        <v>97</v>
+      </c>
+      <c r="AA6" t="s">
+        <v>89</v>
+      </c>
+      <c r="AB6" t="s">
+        <v>98</v>
+      </c>
+      <c r="AC6" t="s">
+        <v>44</v>
+      </c>
+      <c r="AD6" t="s">
+        <v>107</v>
+      </c>
+      <c r="AE6" t="s">
+        <v>116</v>
+      </c>
+      <c r="AF6" t="s">
+        <v>125</v>
+      </c>
+      <c r="AG6" t="s">
+        <v>133</v>
+      </c>
+      <c r="AH6" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="7" spans="1:34">
+      <c r="A7" t="s">
+        <v>34</v>
+      </c>
+      <c r="B7" t="s">
         <v>40</v>
       </c>
-      <c r="H2" t="s">
-        <v>40</v>
-      </c>
-      <c r="I2" t="s">
+      <c r="C7" t="s">
+        <v>45</v>
+      </c>
+      <c r="D7" t="s">
+        <v>51</v>
+      </c>
+      <c r="E7" t="s">
+        <v>59</v>
+      </c>
+      <c r="F7" t="s">
+        <v>62</v>
+      </c>
+      <c r="G7" t="s">
+        <v>63</v>
+      </c>
+      <c r="H7" t="s">
+        <v>63</v>
+      </c>
+      <c r="I7" t="s">
+        <v>65</v>
+      </c>
+      <c r="J7" t="s">
+        <v>71</v>
+      </c>
+      <c r="K7" t="s">
+        <v>71</v>
+      </c>
+      <c r="L7" t="s">
+        <v>74</v>
+      </c>
+      <c r="M7" t="s">
+        <v>83</v>
+      </c>
+      <c r="N7" t="s">
+        <v>85</v>
+      </c>
+      <c r="O7" t="s">
+        <v>87</v>
+      </c>
+      <c r="P7" t="s">
+        <v>88</v>
+      </c>
+      <c r="Q7" t="s">
+        <v>74</v>
+      </c>
+      <c r="R7" t="s">
+        <v>91</v>
+      </c>
+      <c r="S7" t="s">
+        <v>92</v>
+      </c>
+      <c r="T7" t="s">
+        <v>93</v>
+      </c>
+      <c r="U7" t="s">
+        <v>95</v>
+      </c>
+      <c r="V7" t="s">
+        <v>44</v>
+      </c>
+      <c r="W7" t="s">
+        <v>91</v>
+      </c>
+      <c r="X7" t="s">
+        <v>44</v>
+      </c>
+      <c r="Y7" t="s">
+        <v>92</v>
+      </c>
+      <c r="Z7" t="s">
+        <v>97</v>
+      </c>
+      <c r="AA7" t="s">
+        <v>89</v>
+      </c>
+      <c r="AB7" t="s">
+        <v>98</v>
+      </c>
+      <c r="AC7" t="s">
+        <v>101</v>
+      </c>
+      <c r="AD7" t="s">
+        <v>108</v>
+      </c>
+      <c r="AE7" t="s">
+        <v>117</v>
+      </c>
+      <c r="AF7" t="s">
+        <v>126</v>
+      </c>
+      <c r="AG7" t="s">
+        <v>134</v>
+      </c>
+      <c r="AH7" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="8" spans="1:34">
+      <c r="A8" t="s">
+        <v>34</v>
+      </c>
+      <c r="B8" t="s">
         <v>41</v>
       </c>
-      <c r="J2" t="s">
+      <c r="C8" t="s">
+        <v>44</v>
+      </c>
+      <c r="D8" t="s">
+        <v>49</v>
+      </c>
+      <c r="E8" t="s">
+        <v>57</v>
+      </c>
+      <c r="F8" t="s">
+        <v>62</v>
+      </c>
+      <c r="G8" t="s">
+        <v>63</v>
+      </c>
+      <c r="H8" t="s">
+        <v>63</v>
+      </c>
+      <c r="I8" t="s">
+        <v>65</v>
+      </c>
+      <c r="J8" t="s">
+        <v>72</v>
+      </c>
+      <c r="K8" t="s">
+        <v>74</v>
+      </c>
+      <c r="L8" t="s">
+        <v>74</v>
+      </c>
+      <c r="M8" t="s">
+        <v>81</v>
+      </c>
+      <c r="N8" t="s">
+        <v>85</v>
+      </c>
+      <c r="O8" t="s">
+        <v>87</v>
+      </c>
+      <c r="P8" t="s">
+        <v>88</v>
+      </c>
+      <c r="Q8" t="s">
+        <v>74</v>
+      </c>
+      <c r="R8" t="s">
+        <v>91</v>
+      </c>
+      <c r="S8" t="s">
+        <v>92</v>
+      </c>
+      <c r="T8" t="s">
+        <v>93</v>
+      </c>
+      <c r="U8" t="s">
+        <v>95</v>
+      </c>
+      <c r="V8" t="s">
+        <v>44</v>
+      </c>
+      <c r="W8" t="s">
+        <v>91</v>
+      </c>
+      <c r="X8" t="s">
+        <v>44</v>
+      </c>
+      <c r="Y8" t="s">
+        <v>92</v>
+      </c>
+      <c r="Z8" t="s">
+        <v>97</v>
+      </c>
+      <c r="AA8" t="s">
+        <v>89</v>
+      </c>
+      <c r="AB8" t="s">
+        <v>98</v>
+      </c>
+      <c r="AC8" t="s">
+        <v>102</v>
+      </c>
+      <c r="AD8" t="s">
+        <v>109</v>
+      </c>
+      <c r="AE8" t="s">
+        <v>118</v>
+      </c>
+      <c r="AF8" t="s">
+        <v>127</v>
+      </c>
+      <c r="AG8" t="s">
+        <v>135</v>
+      </c>
+      <c r="AH8" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="9" spans="1:34">
+      <c r="A9" t="s">
+        <v>34</v>
+      </c>
+      <c r="B9" t="s">
         <v>42</v>
       </c>
-      <c r="K2" t="s">
-        <v>42</v>
-      </c>
-      <c r="L2" t="s">
-        <v>42</v>
-      </c>
-      <c r="M2" t="s">
-        <v>42</v>
-      </c>
-      <c r="N2" t="s">
+      <c r="C9" t="s">
+        <v>44</v>
+      </c>
+      <c r="D9" t="s">
+        <v>52</v>
+      </c>
+      <c r="E9" t="s">
+        <v>60</v>
+      </c>
+      <c r="F9" t="s">
+        <v>62</v>
+      </c>
+      <c r="G9" t="s">
+        <v>63</v>
+      </c>
+      <c r="H9" t="s">
+        <v>63</v>
+      </c>
+      <c r="I9" t="s">
+        <v>65</v>
+      </c>
+      <c r="J9" t="s">
+        <v>73</v>
+      </c>
+      <c r="K9" t="s">
+        <v>74</v>
+      </c>
+      <c r="L9" t="s">
+        <v>74</v>
+      </c>
+      <c r="M9" t="s">
+        <v>84</v>
+      </c>
+      <c r="N9" t="s">
+        <v>85</v>
+      </c>
+      <c r="O9" t="s">
+        <v>87</v>
+      </c>
+      <c r="P9" t="s">
+        <v>89</v>
+      </c>
+      <c r="Q9" t="s">
+        <v>74</v>
+      </c>
+      <c r="R9" t="s">
+        <v>91</v>
+      </c>
+      <c r="S9" t="s">
+        <v>92</v>
+      </c>
+      <c r="T9" t="s">
+        <v>93</v>
+      </c>
+      <c r="U9" t="s">
+        <v>95</v>
+      </c>
+      <c r="V9" t="s">
+        <v>44</v>
+      </c>
+      <c r="W9" t="s">
+        <v>91</v>
+      </c>
+      <c r="X9" t="s">
+        <v>44</v>
+      </c>
+      <c r="Y9" t="s">
+        <v>92</v>
+      </c>
+      <c r="Z9" t="s">
+        <v>97</v>
+      </c>
+      <c r="AA9" t="s">
+        <v>89</v>
+      </c>
+      <c r="AB9" t="s">
+        <v>98</v>
+      </c>
+      <c r="AC9" t="s">
+        <v>103</v>
+      </c>
+      <c r="AD9" t="s">
+        <v>110</v>
+      </c>
+      <c r="AE9" t="s">
+        <v>119</v>
+      </c>
+      <c r="AF9" t="s">
+        <v>128</v>
+      </c>
+      <c r="AG9" t="s">
+        <v>136</v>
+      </c>
+      <c r="AH9" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="10" spans="1:34">
+      <c r="A10" t="s">
+        <v>34</v>
+      </c>
+      <c r="B10" t="s">
         <v>43</v>
       </c>
-      <c r="O2" t="s">
-        <v>44</v>
-      </c>
-      <c r="P2" t="s">
-        <v>45</v>
-      </c>
-      <c r="Q2" t="s">
-        <v>42</v>
-      </c>
-      <c r="R2" t="s">
-        <v>46</v>
-      </c>
-      <c r="S2" t="s">
-        <v>47</v>
-      </c>
-      <c r="T2" t="s">
-        <v>48</v>
-      </c>
-      <c r="U2" t="s">
-        <v>49</v>
-      </c>
-      <c r="V2" t="s">
-        <v>36</v>
-      </c>
-      <c r="W2" t="s">
-        <v>46</v>
-      </c>
-      <c r="X2" t="s">
-        <v>36</v>
-      </c>
-      <c r="Y2" t="s">
-        <v>47</v>
-      </c>
-      <c r="Z2" t="s">
-        <v>50</v>
-      </c>
-      <c r="AA2" t="s">
-        <v>51</v>
-      </c>
-      <c r="AB2" t="s">
-        <v>52</v>
-      </c>
-      <c r="AC2" t="s">
-        <v>36</v>
-      </c>
-      <c r="AD2" t="s">
+      <c r="C10" t="s">
+        <v>44</v>
+      </c>
+      <c r="D10" t="s">
         <v>53</v>
       </c>
-      <c r="AE2" t="s">
-        <v>54</v>
-      </c>
-      <c r="AF2" t="s">
-        <v>55</v>
-      </c>
-      <c r="AG2" t="s">
-        <v>56</v>
-      </c>
-      <c r="AH2" t="s">
-        <v>57</v>
+      <c r="E10" t="s">
+        <v>61</v>
+      </c>
+      <c r="F10" t="s">
+        <v>62</v>
+      </c>
+      <c r="G10" t="s">
+        <v>63</v>
+      </c>
+      <c r="H10" t="s">
+        <v>63</v>
+      </c>
+      <c r="I10" t="s">
+        <v>65</v>
+      </c>
+      <c r="J10" t="s">
+        <v>74</v>
+      </c>
+      <c r="K10" t="s">
+        <v>74</v>
+      </c>
+      <c r="L10" t="s">
+        <v>74</v>
+      </c>
+      <c r="M10" t="s">
+        <v>74</v>
+      </c>
+      <c r="N10" t="s">
+        <v>86</v>
+      </c>
+      <c r="O10" t="s">
+        <v>87</v>
+      </c>
+      <c r="P10" t="s">
+        <v>88</v>
+      </c>
+      <c r="Q10" t="s">
+        <v>74</v>
+      </c>
+      <c r="R10" t="s">
+        <v>91</v>
+      </c>
+      <c r="S10" t="s">
+        <v>92</v>
+      </c>
+      <c r="T10" t="s">
+        <v>93</v>
+      </c>
+      <c r="U10" t="s">
+        <v>95</v>
+      </c>
+      <c r="V10" t="s">
+        <v>44</v>
+      </c>
+      <c r="W10" t="s">
+        <v>91</v>
+      </c>
+      <c r="X10" t="s">
+        <v>44</v>
+      </c>
+      <c r="Y10" t="s">
+        <v>92</v>
+      </c>
+      <c r="Z10" t="s">
+        <v>97</v>
+      </c>
+      <c r="AA10" t="s">
+        <v>89</v>
+      </c>
+      <c r="AB10" t="s">
+        <v>98</v>
+      </c>
+      <c r="AC10" t="s">
+        <v>44</v>
+      </c>
+      <c r="AD10" t="s">
+        <v>111</v>
+      </c>
+      <c r="AE10" t="s">
+        <v>120</v>
+      </c>
+      <c r="AF10" t="s">
+        <v>129</v>
+      </c>
+      <c r="AG10" t="s">
+        <v>137</v>
+      </c>
+      <c r="AH10" t="s">
+        <v>143</v>
       </c>
     </row>
   </sheetData>
